--- a/90_Threshold_OUTPUT_REPORT/90_best_conclusion_data.xlsx
+++ b/90_Threshold_OUTPUT_REPORT/90_best_conclusion_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,15 +526,20 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Inverted_Pval</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
@@ -590,7 +595,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2683</v>
+        <v>0.2721</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -624,13 +629,18 @@
           <t>GAAGAAAAGGCGA</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
         <v>0.3024790083966413</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.6975209916033587</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -686,7 +696,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -720,13 +730,18 @@
           <t>CGAACAAAAACCGAACA</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
         <v>0.1105557776889244</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -782,7 +797,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -816,13 +831,18 @@
           <t>TTGTTTTGTT</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -878,7 +898,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2258</v>
+        <v>0.179</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -912,13 +932,18 @@
           <t>GAACATATGTTC</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -974,7 +999,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.2619</v>
+        <v>0.2121</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1004,13 +1029,18 @@
           <t>TTACACAGTAA</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>0.05937624950019992</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1066,7 +1096,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.1873</v>
+        <v>0.2385</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1096,13 +1126,18 @@
           <t>CTGTTTTTTTATACAG</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1154,7 +1189,7 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1151</v>
+        <v>0.0638</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1172,15 +1207,16 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1270,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.2333</v>
+        <v>0.235</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1264,13 +1300,18 @@
           <t>TGTTCTCGTTATGTTC</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1326,7 +1367,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.3106</v>
+        <v>0.3162</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1360,13 +1401,18 @@
           <t>TTAATGTCCGGTTAA</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1418,7 +1464,7 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1432,15 +1478,16 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1541,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.2676</v>
+        <v>0.3039</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1524,13 +1571,18 @@
           <t>TCGATC</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
         <v>0.8470611755297881</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.1529388244702119</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1586,7 +1638,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.2575</v>
+        <v>0.2021</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1616,13 +1668,18 @@
           <t>GTGATCTACATCAC</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
         <v>0.0007996801279488205</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.9992003198720512</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1678,7 +1735,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.214</v>
+        <v>0.259</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1712,13 +1769,18 @@
           <t>AGAACAAGTGTTCT</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1774,7 +1836,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.1908</v>
+        <v>0.1948</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1808,13 +1870,18 @@
           <t>AACAAATGTT</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
         <v>0.01819272291083567</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.9818072770891644</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1870,7 +1937,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.2901</v>
+        <v>0.3451</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1904,13 +1971,18 @@
           <t>GACTGTTTTTTTGTACAGTC</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1966,7 +2038,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.2381</v>
+        <v>0.2885</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2000,13 +2072,18 @@
           <t>CTGTATTTATATACAG</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2058,7 +2135,7 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0.1047</v>
+        <v>0.1095</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2072,15 +2149,16 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2212,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.3059</v>
+        <v>0.2507</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -2164,13 +2242,18 @@
           <t>GTTAAAAAAATGTTA</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2226,7 +2309,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.3008</v>
+        <v>0.262</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2256,13 +2339,18 @@
           <t>GTGATCGATATCAC</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2318,7 +2406,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.275</v>
+        <v>0.278</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2352,13 +2440,18 @@
           <t>GTTTATATTTTGTT</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
         <v>0.00819672131147541</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>0.9918032786885246</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2414,7 +2507,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.2061</v>
+        <v>0.2055</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2448,13 +2541,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
         <v>0.2213114754098361</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>0.7786885245901639</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2510,7 +2608,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.2469</v>
+        <v>0.1962</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2544,13 +2642,18 @@
           <t>CAAAGGGGCA</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
         <v>0.1239504198320672</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>0.8760495801679329</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2606,7 +2709,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.2334</v>
+        <v>0.2458</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2640,13 +2743,18 @@
           <t>GGTTGACACATGTAAACC</t>
         </is>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
         <v>0.2387045181927229</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>0.7612954818072771</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2702,7 +2810,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.1946</v>
+        <v>0.1965</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2732,13 +2840,18 @@
           <t>CTGTACATCAATACAG</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2794,7 +2907,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.2098</v>
+        <v>0.1618</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2824,13 +2937,18 @@
           <t>TTTGAAATTCAA</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
         <v>0.04938024790083966</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>0.9506197520991604</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2886,7 +3004,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.2573</v>
+        <v>0.2611</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2920,13 +3038,18 @@
           <t>TTTGCTATACAAA</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
         <v>0.2249100359856057</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2982,7 +3105,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.2563</v>
+        <v>0.2547</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -3012,13 +3135,18 @@
           <t>GAACATATGTTC</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3074,7 +3202,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.2319</v>
+        <v>0.2298</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3108,13 +3236,18 @@
           <t>ACCTAATAAAAATAAGGT</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
         <v>0.009196321471411436</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.9908036785285885</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3170,7 +3303,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.1857</v>
+        <v>0.1893</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3204,13 +3337,18 @@
           <t>AACACATGTT</t>
         </is>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
         <v>0.1273490603758497</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3266,7 +3404,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.1729</v>
+        <v>0.224</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3300,13 +3438,18 @@
           <t>GAACAGGTGTTC</t>
         </is>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
         <v>0.00699720111955218</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3362,7 +3505,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.2784</v>
+        <v>0.2722</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3396,13 +3539,18 @@
           <t>CGAACAGGTGTTCG</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3458,7 +3606,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.2893</v>
+        <v>0.3006</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -3488,13 +3636,18 @@
           <t>TCGAACACATGTTCGA</t>
         </is>
       </c>
-      <c r="T33" t="n">
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3550,7 +3703,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.2663</v>
+        <v>0.2756</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -3580,13 +3733,18 @@
           <t>CTAAAAGCCCGTTCAG</t>
         </is>
       </c>
-      <c r="T34" t="n">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
         <v>0.8048780487804879</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.1951219512195121</v>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3642,7 +3800,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.1727</v>
+        <v>0.1824</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -3672,13 +3830,18 @@
           <t>GTATCATATGATAC</t>
         </is>
       </c>
-      <c r="T35" t="n">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
         <v>0.01839264294282287</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>0.9816073570571772</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3734,7 +3897,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.2403</v>
+        <v>0.2453</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -3764,13 +3927,18 @@
           <t>GTACTTATGT</t>
         </is>
       </c>
-      <c r="T36" t="n">
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
         <v>0.09956017592962815</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>0.9004398240703718</v>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3826,7 +3994,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.1983</v>
+        <v>0.1986</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3860,13 +4028,18 @@
           <t>GAACAACACAGGAAC</t>
         </is>
       </c>
-      <c r="T37" t="n">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
         <v>0.02199120351859256</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>0.9780087964814075</v>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3922,7 +4095,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.2389</v>
+        <v>0.2982</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -3952,13 +4125,18 @@
           <t>CTGTATAAATATACAG</t>
         </is>
       </c>
-      <c r="T38" t="n">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4014,7 +4192,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.2005</v>
+        <v>0.2037</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -4044,13 +4222,18 @@
           <t>GTCACACAACTGTCA</t>
         </is>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4106,7 +4289,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.2567</v>
+        <v>0.31</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -4136,13 +4319,18 @@
           <t>CTGGATATATATACAG</t>
         </is>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4194,7 +4382,7 @@
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>0.0579</v>
+        <v>0.1148</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
@@ -4208,15 +4396,16 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="n">
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>0</v>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4459,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.2433</v>
+        <v>0.2615</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4304,13 +4493,18 @@
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
         <v>0.004198320671731308</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>0.9958016793282687</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4366,7 +4560,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.196</v>
+        <v>0.1947</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4400,13 +4594,18 @@
           <t>GTATCACCCCGGATAC</t>
         </is>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
         <v>0.006797281087564974</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.9932027189124351</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4462,7 +4661,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.2327</v>
+        <v>0.1927</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -4492,13 +4691,18 @@
           <t>GAACAAGACCGGAAC</t>
         </is>
       </c>
-      <c r="T44" t="n">
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4554,7 +4758,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.2919</v>
+        <v>0.2699</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4588,13 +4792,18 @@
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T45" t="n">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4650,7 +4859,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.2393</v>
+        <v>0.1931</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4684,13 +4893,18 @@
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
         <v>0.004198320671731308</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.9958016793282687</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4742,7 +4956,7 @@
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>0.0613</v>
+        <v>0.0644</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4760,15 +4974,16 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="n">
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
         <v>1</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>0</v>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -4822,7 +5037,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.1937</v>
+        <v>0.195</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -4852,13 +5067,18 @@
           <t>AACGCTCCCGAAAC</t>
         </is>
       </c>
-      <c r="T48" t="n">
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4914,7 +5134,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.3266</v>
+        <v>0.2789</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -4944,13 +5164,18 @@
           <t>TTTAGATTTTGTTTA</t>
         </is>
       </c>
-      <c r="T49" t="n">
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
         <v>0.0005997600959616154</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5006,7 +5231,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.1887</v>
+        <v>0.1941</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -5036,13 +5261,18 @@
           <t>GTTAATTAAATGT</t>
         </is>
       </c>
-      <c r="T50" t="n">
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
         <v>0.07976809276289484</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>0.9202319072371051</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5098,7 +5328,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.2318</v>
+        <v>0.2315</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -5128,13 +5358,18 @@
           <t>TTCATAATTTTTCATA</t>
         </is>
       </c>
-      <c r="T51" t="n">
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
         <v>0.002199120351859256</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>0.9978008796481408</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5190,7 +5425,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.23</v>
+        <v>0.2283</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -5220,13 +5455,18 @@
           <t>TCTTGATTTGTTC</t>
         </is>
       </c>
-      <c r="T52" t="n">
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
         <v>0.4520191923230708</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>0.5479808076769292</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5282,7 +5522,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.1763</v>
+        <v>0.1775</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -5312,13 +5552,18 @@
           <t>AACATATGTT</t>
         </is>
       </c>
-      <c r="T53" t="n">
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
         <v>0.04938024790083966</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>0.9506197520991604</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5374,7 +5619,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.238</v>
+        <v>0.1982</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -5404,13 +5649,18 @@
           <t>GTGATCAAGATCAC</t>
         </is>
       </c>
-      <c r="T54" t="n">
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5466,7 +5716,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.3028</v>
+        <v>0.3093</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -5496,13 +5746,18 @@
           <t>GACATAGATC</t>
         </is>
       </c>
-      <c r="T55" t="n">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
         <v>0.02998800479808077</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>0.9700119952019193</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5558,7 +5813,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.3101</v>
+        <v>0.2657</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -5588,13 +5843,18 @@
           <t>CTGTATAAATAAACAG</t>
         </is>
       </c>
-      <c r="T56" t="n">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5650,7 +5910,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -5680,13 +5940,18 @@
           <t>GTGCGCCAAATCAC</t>
         </is>
       </c>
-      <c r="T57" t="n">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
         <v>0.5715713714514195</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5742,7 +6007,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.2406</v>
+        <v>0.2811</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -5772,13 +6037,18 @@
           <t>ATCAATC</t>
         </is>
       </c>
-      <c r="T58" t="n">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5830,7 +6100,7 @@
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
-        <v>0.0885</v>
+        <v>0.1365</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
@@ -5844,15 +6114,16 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
-      <c r="T59" t="n">
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="n">
         <v>1</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>0</v>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -5906,7 +6177,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.2036</v>
+        <v>0.2058</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5940,13 +6211,18 @@
           <t>TGTACAAATGTACA</t>
         </is>
       </c>
-      <c r="T60" t="n">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
         <v>0.003798480607756897</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6002,7 +6278,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -6032,13 +6308,18 @@
           <t>GGTGCGCTTCACCGCACC</t>
         </is>
       </c>
-      <c r="T61" t="n">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
         <v>0.01239504198320672</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6094,7 +6375,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.2483</v>
+        <v>0.2937</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -6124,13 +6405,18 @@
           <t>TGTG</t>
         </is>
       </c>
-      <c r="T62" t="n">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
         <v>0.01679328268692523</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>0.9832067173130747</v>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6186,7 +6472,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.2539</v>
+        <v>0.252</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -6220,13 +6506,18 @@
           <t>TTAGTAAAAATACTAA</t>
         </is>
       </c>
-      <c r="T63" t="n">
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6282,7 +6573,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.2173</v>
+        <v>0.2618</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6316,13 +6607,18 @@
           <t>TTTAATTATTGTT</t>
         </is>
       </c>
-      <c r="T64" t="n">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
         <v>0.08756497401039584</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>0.9124350259896041</v>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6378,7 +6674,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.3206</v>
+        <v>0.2801</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -6408,13 +6704,18 @@
           <t>GTGATTTAGATCAC</t>
         </is>
       </c>
-      <c r="T65" t="n">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6470,7 +6771,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.2464</v>
+        <v>0.2815</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6504,13 +6805,18 @@
           <t>TTTATAATTTGTT</t>
         </is>
       </c>
-      <c r="T66" t="n">
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
         <v>0.08696521391443422</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>0.9130347860855658</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6566,7 +6872,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -6596,13 +6902,18 @@
           <t>CAAGGTGTTAGATTG</t>
         </is>
       </c>
-      <c r="T67" t="n">
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6658,7 +6969,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.2389</v>
+        <v>0.2377</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -6688,13 +6999,18 @@
           <t>TGTAACA</t>
         </is>
       </c>
-      <c r="T68" t="n">
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
         <v>0.01019592163134746</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>0.9898040783686526</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6750,7 +7066,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.237</v>
+        <v>0.2426</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -6780,13 +7096,18 @@
           <t>TTACTTACAAA</t>
         </is>
       </c>
-      <c r="T69" t="n">
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>

--- a/90_Threshold_OUTPUT_REPORT/90_best_conclusion_data.xlsx
+++ b/90_Threshold_OUTPUT_REPORT/90_best_conclusion_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,55 +491,65 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Used Percentile</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Analysis Note</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>coords</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>full_pattern</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Inverted_Pval</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
@@ -595,52 +605,58 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2721</v>
+        <v>0.3854</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>90</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3.999999979202814</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>GAAGAAAAGGCGA</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.3024790083966413</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.6975209916033587</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -696,52 +712,58 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3701</v>
+        <v>1.0858</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>90</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>CGAACAAAAACCGAACA</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.1105557776889244</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -797,52 +819,58 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.5129</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>90</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>[(11, 6), (12, 7), (13, 8), (14, 9), (15, 10)]</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>5</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>9.999999948007035</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>TTGTTTTGTT</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -898,52 +926,58 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.179</v>
+        <v>0.3005</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>90</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>[(9, 4), (10, 3), (11, 2), (12, 1)]</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>4</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>6.620837071970262</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>GTTC</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>GAACATATGTTC</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -999,48 +1033,54 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.2121</v>
+        <v>0.417</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>90</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>[(9, 5), (10, 4), (11, 3), (12, 2)]</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>4</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>TTAC</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>GTAA</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>TTACACAGTAA</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
+        <v>100</v>
+      </c>
+      <c r="W6" t="n">
         <v>0.05937624950019992</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1096,48 +1136,54 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2385</v>
+        <v>0.8417</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>90</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>3</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>CTG</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>CAG</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>CTGTTTTTTTATACAG</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
+        <v>100</v>
+      </c>
+      <c r="W7" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1189,32 +1235,36 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.0638</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>( Caulobacter crescentus NA1000)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>90</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>[DETECT_PATTERNS] - P0CAW8_Caulobacter_crescentus_CB15: Exhausted all fallbacks down to 90th percentile. No diagonal candidates &gt;=2 positions found at user-specified 90%</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>No candidates found</t>
         </is>
@@ -1270,48 +1320,54 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.235</v>
+        <v>0.5223</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>90</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>5</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>7.88838337057375</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>TGTTCTCGTTATGTTC</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>100</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1367,52 +1423,58 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.3162</v>
+        <v>0.4694</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>( Caulobacter crescentus NA1000)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>90</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 2), (14, 3), (15, 4)]</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>4</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>5.299858246910154</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>TTAA</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>TTAA</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>TTAATGTCCGGTTAA</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>100</v>
+      </c>
+      <c r="W10" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1464,28 +1526,32 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0963</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>[DETECT_PATTERNS] - A0A072Z841_Corynebacterium_glutamicum_ATCC_13032: Exhausted all fallbacks down to 90th percentile. No diagonal candidates &gt;=2 positions found at user-specified 90%</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="n">
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>No candidates found</t>
         </is>
@@ -1541,48 +1607,54 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.3039</v>
+        <v>0.4789</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="M12" t="n">
+        <v>90</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>[(16, 12), (17, 13)]</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>2.318206136812991</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>TCGATC</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
+        <v>100</v>
+      </c>
+      <c r="W12" t="n">
         <v>0.8470611755297881</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.1529388244702119</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1638,48 +1710,54 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.2021</v>
+        <v>0.3378</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>3</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>4.322657492525845</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>GTG</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>CAC</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>GTGATCTACATCAC</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.0007996801279488205</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>0.9992003198720512</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1735,52 +1813,58 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.259</v>
+        <v>0.3755</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>90</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>6</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>AGAACA</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>TGTTCT</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>AGAACAAGTGTTCT</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>100</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1836,52 +1920,58 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.1948</v>
+        <v>0.3355</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>[(8, 5), (9, 4), (10, 3), (11, 2)]</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>4</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>AACA</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>TGTT</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>AACAAATGTT</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
+        <v>100</v>
+      </c>
+      <c r="W15" t="n">
         <v>0.01819272291083567</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.9818072770891644</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1937,52 +2027,58 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.3451</v>
+        <v>0.524</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>[Escherichia coli str. K-12 substr. MG1655]</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>90</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>[(14, 5), (15, 4), (16, 3), (17, 2), (18, 1), (19, 0)]</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>6</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>GACTGT</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>ACAGTC</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>GACTGTTTTTTTGTACAGTC</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
+        <v>100</v>
+      </c>
+      <c r="W16" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2038,52 +2134,58 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.2885</v>
+        <v>0.4304</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>[Escherichia coli str. K-12 substr. MG1655]</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>[(15, 4), (16, 3), (17, 2)]</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>5.360098288403806</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>CTG</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>CAG</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>CTGTATTTATATACAG</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
+        <v>100</v>
+      </c>
+      <c r="W17" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2135,28 +2237,32 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0.1095</v>
+        <v>0.126</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>90</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>[DETECT_PATTERNS] - P0A9E5_Escherichia_coli_str__K-12_substr__MG1655: Exhausted all fallbacks down to 90th percentile. No diagonal candidates &gt;=2 positions found at user-specified 90%</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
         <v>1</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>No candidates found</t>
         </is>
@@ -2212,48 +2318,54 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.2507</v>
+        <v>0.4395</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>90</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>5.201745855169004</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>GTTA</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>GTTA</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>GTTAAAAAAATGTTA</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
+        <v>100</v>
+      </c>
+      <c r="W19" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2309,48 +2421,54 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.262</v>
+        <v>0.4701</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="M20" t="n">
+        <v>90</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>[(14, 7), (15, 6), (16, 5), (17, 4)]</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>4</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>5.64665317530554</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>GTGA</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>TCAC</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>GTGATCGATATCAC</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
+        <v>100</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2406,52 +2524,58 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.278</v>
+        <v>0.4867</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>(Escherichia coli str. K-12 substr. W3110)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="M21" t="n">
+        <v>90</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>[(15, 4), (16, 5), (17, 6)]</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>3</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>3.628722119655927</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>GTT</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>GTT</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>GTTTATATTTTGTT</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
+        <v>100</v>
+      </c>
+      <c r="W21" t="n">
         <v>0.00819672131147541</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.9918032786885246</v>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2507,52 +2631,58 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.2055</v>
+        <v>0.3562</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>(Escherichia coli str. K-12 substr. W3110)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>90</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>[(3, 2), (4, 3)]</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>3.632542292952781</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
+        <v>100</v>
+      </c>
+      <c r="W22" t="n">
         <v>0.2213114754098361</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.7786885245901639</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2608,52 +2738,58 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.1962</v>
+        <v>0.3325</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>(https://www.microbiologyresearch.org/content/journal/micro/10.1099/mic.0.27315-0)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="M23" t="n">
+        <v>90</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>[(13, 5), (14, 6)]</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>3.422972844335447</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>CAAAGGGGCA</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
+        <v>100</v>
+      </c>
+      <c r="W23" t="n">
         <v>0.1239504198320672</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.8760495801679329</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2709,52 +2845,58 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.2458</v>
+        <v>0.4042</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="M24" t="n">
+        <v>90</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>[(15, 2), (16, 1), (17, 0)]</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>3</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>GGT</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>GGTTGACACATGTAAACC</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
+        <v>100</v>
+      </c>
+      <c r="W24" t="n">
         <v>0.2387045181927229</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.7612954818072771</v>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2810,48 +2952,54 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.1965</v>
+        <v>0.329</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="M25" t="n">
+        <v>90</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>3</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>CTG</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>CAG</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>CTGTACATCAATACAG</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
+        <v>100</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2907,48 +3055,54 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.1618</v>
+        <v>0.2692</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="M26" t="n">
+        <v>90</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>[(10, 1), (11, 0)]</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>3.999999979202814</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>TTTGAAATTCAA</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
+        <v>100</v>
+      </c>
+      <c r="W26" t="n">
         <v>0.04938024790083966</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.9506197520991604</v>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3004,52 +3158,58 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.2611</v>
+        <v>0.357</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="n">
+        <v>90</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>[(9, 3), (10, 2), (11, 1), (12, 0)]</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>4</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>TTTG</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>CAAA</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>TTTGCTATACAAA</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
+        <v>100</v>
+      </c>
+      <c r="W27" t="n">
         <v>0.2249100359856057</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3105,48 +3265,54 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.2547</v>
+        <v>0.4362</v>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>90</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>[(14, 7), (15, 6), (16, 5)]</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>3</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>5.340066379077927</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>GAA</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>TTC</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>GAACATATGTTC</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
+        <v>100</v>
+      </c>
+      <c r="W28" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3202,52 +3368,58 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.2298</v>
+        <v>0.4</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="M29" t="n">
+        <v>90</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
         <is>
           <t>[(14, 3), (15, 2), (16, 1), (17, 0)]</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>4</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>ACCT</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>AGGT</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>ACCTAATAAAAATAAGGT</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
+        <v>100</v>
+      </c>
+      <c r="W29" t="n">
         <v>0.009196321471411436</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.9908036785285885</v>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3303,52 +3475,58 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.1893</v>
+        <v>0.3146</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="M30" t="n">
+        <v>90</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
         <is>
           <t>[(7, 4), (8, 3), (9, 2), (10, 1)]</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>4</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>AACA</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>TGTT</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>AACACATGTT</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
+        <v>100</v>
+      </c>
+      <c r="W30" t="n">
         <v>0.1273490603758497</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3404,52 +3582,58 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.224</v>
+        <v>0.3002</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>90</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>[(7, 4), (8, 3), (9, 2), (10, 1), (11, 0)]</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>5</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>9.999999948007035</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>GAACA</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>GAACAGGTGTTC</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
+        <v>100</v>
+      </c>
+      <c r="W31" t="n">
         <v>0.00699720111955218</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3505,52 +3689,58 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.2722</v>
+        <v>0.4044</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="M32" t="n">
+        <v>90</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>[(9, 6), (10, 5), (11, 4), (12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>6</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>TGTTCG</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>CGAACAGGTGTTCG</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
+        <v>100</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3606,48 +3796,54 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.3006</v>
+        <v>0.4379</v>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="M33" t="n">
+        <v>90</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>[(13, 6), (14, 5), (15, 4), (16, 3), (17, 2)]</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>5</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>7.94108534992435</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>TCGAA</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>TTCGA</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>TCGAACACATGTTCGA</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
+        <v>100</v>
+      </c>
+      <c r="W33" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3703,48 +3899,54 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.2756</v>
+        <v>0.3659</v>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="M34" t="n">
+        <v>90</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>[(14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.999999979202814</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>CTAAAAGCCCGTTCAG</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
+        <v>100</v>
+      </c>
+      <c r="W34" t="n">
         <v>0.8048780487804879</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.1951219512195121</v>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3800,48 +4002,54 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.1824</v>
+        <v>0.3094</v>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="M35" t="n">
+        <v>90</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>[(12, 1), (13, 0)]</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.521546164531683</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>GTATCATATGATAC</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" t="n">
         <v>0.01839264294282287</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.9816073570571772</v>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -3897,48 +4105,54 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.2453</v>
+        <v>0.3357</v>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="n">
+        <v>90</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>[(10, 2), (11, 3)]</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.999999979202814</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>GTACTTATGT</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
+        <v>100</v>
+      </c>
+      <c r="W36" t="n">
         <v>0.09956017592962815</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.9004398240703718</v>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3994,52 +4208,58 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.1986</v>
+        <v>0.6879</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="M37" t="n">
+        <v>90</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>4</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>GAACAACACAGGAAC</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
+        <v>100</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.02199120351859256</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.9780087964814075</v>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4095,48 +4315,54 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.2982</v>
+        <v>0.41</v>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="n">
+        <v>90</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>[(15, 4), (16, 3), (17, 2)]</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>3</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>CTG</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>CAG</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>CTGTATAAATATACAG</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
+        <v>100</v>
+      </c>
+      <c r="W38" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4192,48 +4418,54 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.2037</v>
+        <v>0.3436</v>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="M39" t="n">
+        <v>90</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>4</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>5.695953897370262</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>GTCA</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>GTCA</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>GTCACACAACTGTCA</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
+        <v>100</v>
+      </c>
+      <c r="W39" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4289,48 +4521,54 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.31</v>
+        <v>0.4651</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="n">
+        <v>90</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>[(16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>CTG</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>CAG</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>CTGGATATATATACAG</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
+        <v>100</v>
+      </c>
+      <c r="W40" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4382,28 +4620,32 @@
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>0.1148</v>
+        <v>0.0888</v>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="n">
+        <v>90</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>[DETECT_PATTERNS] - Q88F34_Pseudomonas_putida_KT2440: Exhausted all fallbacks down to 90th percentile. No diagonal candidates &gt;=2 positions found at user-specified 90%</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="n">
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
         <v>1</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0</v>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>No candidates found</t>
         </is>
@@ -4459,52 +4701,58 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.2615</v>
+        <v>0.3418</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>(https://pmc.ncbi.nlm.nih.gov/articles/PMC2689224/)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="n">
+        <v>90</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>[(9, 8), (10, 9), (11, 10), (12, 11)]</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>4</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>TTTT</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>TTTT</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
+        <v>100</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.004198320671731308</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.9958016793282687</v>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4560,52 +4808,58 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.1947</v>
+        <v>0.3373</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>(?? https://apsjournals.apsnet.org/doi/pdf/10.1094/MPMI-23-7-0927)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="M43" t="n">
+        <v>90</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>3</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>5.497377483821777</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>GTA</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>TAC</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>GTATCACCCCGGATAC</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
+        <v>100</v>
+      </c>
+      <c r="W43" t="n">
         <v>0.006797281087564974</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>0.9932027189124351</v>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4661,48 +4915,54 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.1927</v>
+        <v>0.3173</v>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="M44" t="n">
+        <v>90</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>4</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>7.42297282353826</v>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>GAACAAGACCGGAAC</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
+        <v>100</v>
+      </c>
+      <c r="W44" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4758,52 +5018,58 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.2699</v>
+        <v>0.4034</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="M45" t="n">
+        <v>90</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>4</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
+        <v>100</v>
+      </c>
+      <c r="W45" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4859,52 +5125,58 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.1931</v>
+        <v>0.3356</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="M46" t="n">
+        <v>90</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1), (13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>4</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>GAAC</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
+        <v>100</v>
+      </c>
+      <c r="W46" t="n">
         <v>0.004198320671731308</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>0.9958016793282687</v>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4956,32 +5228,36 @@
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>0.0644</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" t="n">
+        <v>90</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>[DETECT_PATTERNS] - Q9ZFA4_Rhodobacter_sphaeroides_ATCC_17029: Exhausted all fallbacks down to 90th percentile. No diagonal candidates &gt;=2 positions found at user-specified 90%</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="n">
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
+      <c r="X47" t="n">
         <v>0</v>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>No candidates found</t>
         </is>
@@ -5037,48 +5313,54 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.195</v>
+        <v>0.3245</v>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="M48" t="n">
+        <v>90</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3), (15, 4)]</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>3</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>3.485881343809507</v>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>AACGCTCCCGAAAC</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
+        <v>100</v>
+      </c>
+      <c r="W48" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="V48" t="n">
+      <c r="X48" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5134,48 +5416,54 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.2789</v>
+        <v>0.4962</v>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="M49" t="n">
+        <v>90</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
         <is>
           <t>[(16, 5), (17, 6), (18, 7), (19, 8)]</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>4</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>5.261153008134427</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>TTTA</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>TTTA</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>TTTAGATTTTGTTTA</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
+        <v>100</v>
+      </c>
+      <c r="W49" t="n">
         <v>0.0005997600959616154</v>
       </c>
-      <c r="V49" t="n">
+      <c r="X49" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5231,48 +5519,54 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.1941</v>
+        <v>0.3198</v>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="M50" t="n">
+        <v>90</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>[(11, 0), (12, 1)]</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>3.375306912419876</v>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>GTTAATTAAATGT</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
+        <v>100</v>
+      </c>
+      <c r="W50" t="n">
         <v>0.07976809276289484</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>0.9202319072371051</v>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5328,48 +5622,54 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.2315</v>
+        <v>0.401</v>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="M51" t="n">
+        <v>90</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
         <is>
           <t>[(10, 0), (11, 1), (12, 2), (13, 3), (14, 4), (15, 5)]</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>6</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>TTCATA</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>TTCATA</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>TTCATAATTTTTCATA</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
+        <v>100</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.002199120351859256</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>0.9978008796481408</v>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5425,48 +5725,54 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.2283</v>
+        <v>0.4289</v>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="M52" t="n">
+        <v>90</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
         <is>
           <t>[(15, 4), (16, 5)]</t>
         </is>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>3.531004388919936</v>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>TCTTGATTTGTTC</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
+        <v>100</v>
+      </c>
+      <c r="W52" t="n">
         <v>0.4520191923230708</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>0.5479808076769292</v>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -5522,48 +5828,54 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.1775</v>
+        <v>0.9462</v>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="M53" t="n">
+        <v>90</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
         <is>
           <t>[(10, 3), (11, 2)]</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>3.999999979202814</v>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>AACATATGTT</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
+        <v>100</v>
+      </c>
+      <c r="W53" t="n">
         <v>0.04938024790083966</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>0.9506197520991604</v>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5619,48 +5931,54 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.1982</v>
+        <v>0.3359</v>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="M54" t="n">
+        <v>90</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
         <is>
           <t>[(11, 4), (12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>4</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>7.999999958405628</v>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>GTGA</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>TCAC</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>GTGATCAAGATCAC</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
+        <v>100</v>
+      </c>
+      <c r="W54" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5716,48 +6034,54 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.3093</v>
+        <v>0.4527</v>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="M55" t="n">
+        <v>90</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
         <is>
           <t>[(14, 7), (15, 6)]</t>
         </is>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>2</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>3.999999979202814</v>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>GACATAGATC</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
+        <v>100</v>
+      </c>
+      <c r="W55" t="n">
         <v>0.02998800479808077</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0.9700119952019193</v>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5813,48 +6137,54 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.2657</v>
+        <v>0.4688</v>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
+      <c r="M56" t="n">
+        <v>90</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
         <is>
           <t>[(15, 6), (16, 5), (17, 4), (18, 3)]</t>
         </is>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>4</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>7.531004368122749</v>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>CTGT</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>ACAG</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>CTGTATAAATAAACAG</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
+        <v>100</v>
+      </c>
+      <c r="W56" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -5910,48 +6240,54 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.2563</v>
+        <v>0.4559</v>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="M57" t="n">
+        <v>90</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
         <is>
           <t>[(12, 3), (13, 2), (14, 1)]</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>GTG</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>CAC</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>GTGCGCCAAATCAC</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
+        <v>100</v>
+      </c>
+      <c r="W57" t="n">
         <v>0.5715713714514195</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6007,48 +6343,54 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.2811</v>
+        <v>0.393</v>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="M58" t="n">
+        <v>90</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
         <is>
           <t>[(10, 6), (11, 7), (12, 8)]</t>
         </is>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>ATC</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>ATC</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>ATCAATC</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
+        <v>100</v>
+      </c>
+      <c r="W58" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="V58" t="n">
+      <c r="X58" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -6100,28 +6442,32 @@
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
-        <v>0.1365</v>
+        <v>0.1513</v>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
+      <c r="M59" t="n">
+        <v>90</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>[DETECT_PATTERNS] - Q7M7I9_Vibrio_vulnificus_YJ016: Exhausted all fallbacks down to 90th percentile. No diagonal candidates &gt;=2 positions found at user-specified 90%</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="n">
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="n">
         <v>1</v>
       </c>
-      <c r="V59" t="n">
+      <c r="X59" t="n">
         <v>0</v>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>No candidates found</t>
         </is>
@@ -6177,52 +6523,58 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.2058</v>
+        <v>0.3537</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>(1 seq)</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
+      <c r="M60" t="n">
+        <v>90</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>[(8, 0), (9, 1), (10, 2), (11, 3), (12, 4), (13, 5)]</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>6</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>TGTACAAATGTACA</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
+        <v>100</v>
+      </c>
+      <c r="W60" t="n">
         <v>0.003798480607756897</v>
       </c>
-      <c r="V60" t="n">
+      <c r="X60" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6278,48 +6630,54 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.3632</v>
+        <v>0.6655</v>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="M61" t="n">
+        <v>90</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
         <is>
           <t>[(15, 8), (16, 7), (17, 6), (18, 5), (19, 4), (20, 3)]</t>
         </is>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>6</v>
       </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>GGTGCG</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>CGCACC</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>GGTGCGCTTCACCGCACC</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
+        <v>100</v>
+      </c>
+      <c r="W61" t="n">
         <v>0.01239504198320672</v>
       </c>
-      <c r="V61" t="n">
+      <c r="X61" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6375,48 +6733,54 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.2937</v>
+        <v>0.4561</v>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
+      <c r="M62" t="n">
+        <v>90</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
         <is>
           <t>[(5, 3), (6, 4)]</t>
         </is>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>2</v>
       </c>
-      <c r="P62" t="n">
+      <c r="Q62" t="n">
         <v>3.062209303013574</v>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>TGTG</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
+        <v>100</v>
+      </c>
+      <c r="W62" t="n">
         <v>0.01679328268692523</v>
       </c>
-      <c r="V62" t="n">
+      <c r="X62" t="n">
         <v>0.9832067173130747</v>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -6472,52 +6836,58 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.252</v>
+        <v>0.4412</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>(2 seq)</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
+      <c r="M63" t="n">
+        <v>90</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
         <is>
           <t>[(10, 5), (11, 4), (12, 3), (13, 2), (14, 1), (15, 0)]</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>6</v>
       </c>
-      <c r="P63" t="n">
+      <c r="Q63" t="n">
         <v>11.99999993760844</v>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>TTAGTA</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>TACTAA</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>TTAGTAAAAATACTAA</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
+        <v>100</v>
+      </c>
+      <c r="W63" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="V63" t="n">
+      <c r="X63" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6573,52 +6943,58 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.2618</v>
+        <v>0.3843</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>(Yersinia pestis KIM10+)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
+      <c r="M64" t="n">
+        <v>90</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
         <is>
           <t>[(13, 2), (14, 3)]</t>
         </is>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>2</v>
       </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
         <v>2.025248260095768</v>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>TTTAATTATTGTT</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
+        <v>100</v>
+      </c>
+      <c r="W64" t="n">
         <v>0.08756497401039584</v>
       </c>
-      <c r="V64" t="n">
+      <c r="X64" t="n">
         <v>0.9124350259896041</v>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6674,48 +7050,54 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.2801</v>
+        <v>0.499</v>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
+      <c r="M65" t="n">
+        <v>90</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
         <is>
           <t>[(15, 8), (16, 7), (17, 6), (18, 5)]</t>
         </is>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>4</v>
       </c>
-      <c r="P65" t="n">
+      <c r="Q65" t="n">
         <v>5.635422657742285</v>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>GTGA</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>TCAC</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>GTGATTTAGATCAC</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
+        <v>100</v>
+      </c>
+      <c r="W65" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="V65" t="n">
+      <c r="X65" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -6771,52 +7153,58 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.2815</v>
+        <v>0.4003</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>(Yersinia pestis KIM10+)</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
+      <c r="M66" t="n">
+        <v>90</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
         <is>
           <t>[(14, 3), (15, 4)]</t>
         </is>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>2</v>
       </c>
-      <c r="P66" t="n">
+      <c r="Q66" t="n">
         <v>3.843397716666898</v>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>TTTATAATTTGTT</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>Confirmed DR</t>
         </is>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
+        <v>100</v>
+      </c>
+      <c r="W66" t="n">
         <v>0.08696521391443422</v>
       </c>
-      <c r="V66" t="n">
+      <c r="X66" t="n">
         <v>0.9130347860855658</v>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6872,48 +7260,54 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.746</v>
+        <v>1.627</v>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
+      <c r="M67" t="n">
+        <v>90</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
         <is>
           <t>[(14, 4), (15, 3), (16, 2)]</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>3</v>
       </c>
-      <c r="P67" t="n">
+      <c r="Q67" t="n">
         <v>5.999999968804222</v>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>CAA</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>TTG</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>CAAGGTGTTAGATTG</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
+        <v>100</v>
+      </c>
+      <c r="W67" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="V67" t="n">
+      <c r="X67" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6969,48 +7363,54 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.2377</v>
+        <v>0.4111</v>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
+      <c r="M68" t="n">
+        <v>90</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
         <is>
           <t>[(13, 11), (14, 10), (15, 9)]</t>
         </is>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>3</v>
       </c>
-      <c r="P68" t="n">
+      <c r="Q68" t="n">
         <v>3.271546368780269</v>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>ACA</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>TGTAACA</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
+        <v>100</v>
+      </c>
+      <c r="W68" t="n">
         <v>0.01019592163134746</v>
       </c>
-      <c r="V68" t="n">
+      <c r="X68" t="n">
         <v>0.9898040783686526</v>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -7066,48 +7466,54 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.2426</v>
+        <v>0.4167</v>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
+      <c r="M69" t="n">
+        <v>90</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
         <is>
           <t>[(10, 2), (11, 1)]</t>
         </is>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>2</v>
       </c>
-      <c r="P69" t="n">
+      <c r="Q69" t="n">
         <v>3.999999979202814</v>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>TTACTTACAAA</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>Confirmed IR</t>
         </is>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
+        <v>100</v>
+      </c>
+      <c r="W69" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="V69" t="n">
+      <c r="X69" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
